--- a/Scaling Tests.xlsx
+++ b/Scaling Tests.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edubuas.sharepoint.com/teams/2024-25MGT37/Shared Documents/General/Hidde Derks - 200170/Working Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MGT-2025-26\MGT-Thesis-Repository\MGT-Thesis-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="8_{E80829E9-B0B7-4F25-A441-8C6B60E39F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C784B8-4840-41C6-A831-63A0370685EC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0B250F-5303-4254-BA2A-059F9699D35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2151,11 +2151,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2163,19 +2166,16 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7376,7 +7376,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Cores / Agent</a:t>
+                  <a:t>Agents</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -15832,7 +15832,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
@@ -15862,7 +15862,7 @@
       <c r="J2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="L2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="3">
@@ -15892,7 +15892,7 @@
       <c r="U2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W2" s="52" t="s">
+      <c r="W2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="X2" s="3">
@@ -15924,7 +15924,7 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
+      <c r="A3" s="55"/>
       <c r="B3" s="5">
         <v>32</v>
       </c>
@@ -15952,7 +15952,7 @@
       <c r="J3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="52"/>
+      <c r="L3" s="55"/>
       <c r="M3" s="5">
         <v>32</v>
       </c>
@@ -15980,7 +15980,7 @@
       <c r="U3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="W3" s="52"/>
+      <c r="W3" s="55"/>
       <c r="X3" s="5">
         <v>32</v>
       </c>
@@ -16010,7 +16010,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
+      <c r="A4" s="55"/>
       <c r="B4" s="7">
         <v>32</v>
       </c>
@@ -16038,7 +16038,7 @@
       <c r="J4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="52"/>
+      <c r="L4" s="55"/>
       <c r="M4" s="7">
         <v>32</v>
       </c>
@@ -16066,7 +16066,7 @@
       <c r="U4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="52"/>
+      <c r="W4" s="55"/>
       <c r="X4" s="7">
         <v>32</v>
       </c>
@@ -16096,7 +16096,7 @@
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="5">
         <v>32</v>
       </c>
@@ -16124,7 +16124,7 @@
       <c r="J5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="52"/>
+      <c r="L5" s="55"/>
       <c r="M5" s="5">
         <v>32</v>
       </c>
@@ -16152,7 +16152,7 @@
       <c r="U5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="W5" s="52"/>
+      <c r="W5" s="55"/>
       <c r="X5" s="5">
         <v>32</v>
       </c>
@@ -16182,7 +16182,7 @@
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="7">
         <v>16</v>
       </c>
@@ -16210,7 +16210,7 @@
       <c r="J6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="52"/>
+      <c r="L6" s="55"/>
       <c r="M6" s="7">
         <v>16</v>
       </c>
@@ -16238,7 +16238,7 @@
       <c r="U6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="W6" s="52"/>
+      <c r="W6" s="55"/>
       <c r="X6" s="7">
         <v>16</v>
       </c>
@@ -16268,7 +16268,7 @@
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="5">
         <v>16</v>
       </c>
@@ -16296,7 +16296,7 @@
       <c r="J7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="52"/>
+      <c r="L7" s="55"/>
       <c r="M7" s="5">
         <v>16</v>
       </c>
@@ -16324,7 +16324,7 @@
       <c r="U7" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="W7" s="52"/>
+      <c r="W7" s="55"/>
       <c r="X7" s="5">
         <v>16</v>
       </c>
@@ -16354,7 +16354,7 @@
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
+      <c r="A8" s="55"/>
       <c r="B8" s="7">
         <v>16</v>
       </c>
@@ -16382,7 +16382,7 @@
       <c r="J8" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="52"/>
+      <c r="L8" s="55"/>
       <c r="M8" s="7">
         <v>16</v>
       </c>
@@ -16410,7 +16410,7 @@
       <c r="U8" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="W8" s="52"/>
+      <c r="W8" s="55"/>
       <c r="X8" s="7">
         <v>16</v>
       </c>
@@ -16440,7 +16440,7 @@
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="5">
         <v>16</v>
       </c>
@@ -16468,7 +16468,7 @@
       <c r="J9" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="L9" s="52"/>
+      <c r="L9" s="55"/>
       <c r="M9" s="5">
         <v>16</v>
       </c>
@@ -16496,7 +16496,7 @@
       <c r="U9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="W9" s="52"/>
+      <c r="W9" s="55"/>
       <c r="X9" s="5">
         <v>16</v>
       </c>
@@ -16526,7 +16526,7 @@
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="7">
         <v>64</v>
       </c>
@@ -16554,7 +16554,7 @@
       <c r="J10" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="L10" s="52"/>
+      <c r="L10" s="55"/>
       <c r="M10" s="7">
         <v>64</v>
       </c>
@@ -16582,7 +16582,7 @@
       <c r="U10" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="W10" s="52"/>
+      <c r="W10" s="55"/>
       <c r="X10" s="7">
         <v>64</v>
       </c>
@@ -16612,7 +16612,7 @@
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="5">
         <v>64</v>
       </c>
@@ -16640,7 +16640,7 @@
       <c r="J11" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="L11" s="52"/>
+      <c r="L11" s="55"/>
       <c r="M11" s="5">
         <v>64</v>
       </c>
@@ -16668,7 +16668,7 @@
       <c r="U11" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="W11" s="52"/>
+      <c r="W11" s="55"/>
       <c r="X11" s="5">
         <v>64</v>
       </c>
@@ -16698,7 +16698,7 @@
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="7">
         <v>64</v>
       </c>
@@ -16726,7 +16726,7 @@
       <c r="J12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="L12" s="52"/>
+      <c r="L12" s="55"/>
       <c r="M12" s="7">
         <v>64</v>
       </c>
@@ -16754,7 +16754,7 @@
       <c r="U12" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="W12" s="52"/>
+      <c r="W12" s="55"/>
       <c r="X12" s="7">
         <v>64</v>
       </c>
@@ -16784,7 +16784,7 @@
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="55"/>
       <c r="B13" s="5">
         <v>64</v>
       </c>
@@ -16812,7 +16812,7 @@
       <c r="J13" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="52"/>
+      <c r="L13" s="55"/>
       <c r="M13" s="5">
         <v>64</v>
       </c>
@@ -16840,7 +16840,7 @@
       <c r="U13" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="W13" s="52"/>
+      <c r="W13" s="55"/>
       <c r="X13" s="5">
         <v>64</v>
       </c>
@@ -16870,7 +16870,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="55"/>
       <c r="B14" s="7">
         <v>8</v>
       </c>
@@ -16898,7 +16898,7 @@
       <c r="J14" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="L14" s="52"/>
+      <c r="L14" s="55"/>
       <c r="M14" s="7">
         <v>8</v>
       </c>
@@ -16926,7 +16926,7 @@
       <c r="U14" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="W14" s="52"/>
+      <c r="W14" s="55"/>
       <c r="X14" s="7">
         <v>8</v>
       </c>
@@ -16956,7 +16956,7 @@
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="55"/>
       <c r="B15" s="5">
         <v>8</v>
       </c>
@@ -16984,7 +16984,7 @@
       <c r="J15" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="L15" s="52"/>
+      <c r="L15" s="55"/>
       <c r="M15" s="5">
         <v>8</v>
       </c>
@@ -17012,7 +17012,7 @@
       <c r="U15" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="W15" s="52"/>
+      <c r="W15" s="55"/>
       <c r="X15" s="5">
         <v>8</v>
       </c>
@@ -17042,7 +17042,7 @@
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="55"/>
       <c r="B16" s="7">
         <v>8</v>
       </c>
@@ -17070,7 +17070,7 @@
       <c r="J16" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L16" s="52"/>
+      <c r="L16" s="55"/>
       <c r="M16" s="7">
         <v>8</v>
       </c>
@@ -17098,7 +17098,7 @@
       <c r="U16" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="W16" s="52"/>
+      <c r="W16" s="55"/>
       <c r="X16" s="7">
         <v>8</v>
       </c>
@@ -17128,7 +17128,7 @@
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="55"/>
       <c r="B17" s="5">
         <v>8</v>
       </c>
@@ -17156,7 +17156,7 @@
       <c r="J17" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="L17" s="52"/>
+      <c r="L17" s="55"/>
       <c r="M17" s="5">
         <v>8</v>
       </c>
@@ -17184,7 +17184,7 @@
       <c r="U17" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="W17" s="52"/>
+      <c r="W17" s="55"/>
       <c r="X17" s="5">
         <v>8</v>
       </c>
@@ -17214,7 +17214,7 @@
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A18" s="52"/>
+      <c r="A18" s="55"/>
       <c r="B18" s="7">
         <v>4</v>
       </c>
@@ -17242,7 +17242,7 @@
       <c r="J18" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="L18" s="52"/>
+      <c r="L18" s="55"/>
       <c r="M18" s="7">
         <v>4</v>
       </c>
@@ -17270,7 +17270,7 @@
       <c r="U18" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="W18" s="52"/>
+      <c r="W18" s="55"/>
       <c r="X18" s="7">
         <v>4</v>
       </c>
@@ -17300,7 +17300,7 @@
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="5">
         <v>4</v>
       </c>
@@ -17328,7 +17328,7 @@
       <c r="J19" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="L19" s="52"/>
+      <c r="L19" s="55"/>
       <c r="M19" s="5">
         <v>4</v>
       </c>
@@ -17356,7 +17356,7 @@
       <c r="U19" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="W19" s="52"/>
+      <c r="W19" s="55"/>
       <c r="X19" s="5">
         <v>4</v>
       </c>
@@ -17386,7 +17386,7 @@
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="7">
         <v>4</v>
       </c>
@@ -17414,7 +17414,7 @@
       <c r="J20" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="L20" s="52"/>
+      <c r="L20" s="55"/>
       <c r="M20" s="7">
         <v>4</v>
       </c>
@@ -17442,7 +17442,7 @@
       <c r="U20" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="W20" s="52"/>
+      <c r="W20" s="55"/>
       <c r="X20" s="7">
         <v>4</v>
       </c>
@@ -17472,7 +17472,7 @@
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="5">
         <v>4</v>
       </c>
@@ -17500,7 +17500,7 @@
       <c r="J21" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="L21" s="52"/>
+      <c r="L21" s="55"/>
       <c r="M21" s="5">
         <v>4</v>
       </c>
@@ -17528,7 +17528,7 @@
       <c r="U21" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="W21" s="52"/>
+      <c r="W21" s="55"/>
       <c r="X21" s="5">
         <v>4</v>
       </c>
@@ -17644,7 +17644,7 @@
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="55" t="s">
         <v>180</v>
       </c>
       <c r="B23" s="3">
@@ -17674,7 +17674,7 @@
       <c r="J23" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L23" s="52" t="s">
+      <c r="L23" s="55" t="s">
         <v>180</v>
       </c>
       <c r="M23" s="3">
@@ -17704,7 +17704,7 @@
       <c r="U23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="W23" s="52" t="s">
+      <c r="W23" s="55" t="s">
         <v>180</v>
       </c>
       <c r="X23" s="3">
@@ -17736,7 +17736,7 @@
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="5">
         <v>4</v>
       </c>
@@ -17764,7 +17764,7 @@
       <c r="J24" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="L24" s="52"/>
+      <c r="L24" s="55"/>
       <c r="M24" s="5">
         <v>4</v>
       </c>
@@ -17792,7 +17792,7 @@
       <c r="U24" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="W24" s="52"/>
+      <c r="W24" s="55"/>
       <c r="X24" s="5">
         <v>4</v>
       </c>
@@ -17822,7 +17822,7 @@
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A25" s="52"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="7">
         <v>4</v>
       </c>
@@ -17850,7 +17850,7 @@
       <c r="J25" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L25" s="52"/>
+      <c r="L25" s="55"/>
       <c r="M25" s="7">
         <v>4</v>
       </c>
@@ -17878,7 +17878,7 @@
       <c r="U25" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="W25" s="52"/>
+      <c r="W25" s="55"/>
       <c r="X25" s="7">
         <v>4</v>
       </c>
@@ -17908,7 +17908,7 @@
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="5">
         <v>4</v>
       </c>
@@ -17936,7 +17936,7 @@
       <c r="J26" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="L26" s="52"/>
+      <c r="L26" s="55"/>
       <c r="M26" s="5">
         <v>4</v>
       </c>
@@ -17964,7 +17964,7 @@
       <c r="U26" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="W26" s="52"/>
+      <c r="W26" s="55"/>
       <c r="X26" s="5">
         <v>4</v>
       </c>
@@ -17994,7 +17994,7 @@
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
+      <c r="A27" s="55"/>
       <c r="B27" s="7">
         <v>8</v>
       </c>
@@ -18022,7 +18022,7 @@
       <c r="J27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="L27" s="52"/>
+      <c r="L27" s="55"/>
       <c r="M27" s="7">
         <v>8</v>
       </c>
@@ -18050,7 +18050,7 @@
       <c r="U27" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="W27" s="52"/>
+      <c r="W27" s="55"/>
       <c r="X27" s="7">
         <v>8</v>
       </c>
@@ -18080,7 +18080,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="55"/>
       <c r="B28" s="5">
         <v>8</v>
       </c>
@@ -18108,7 +18108,7 @@
       <c r="J28" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="L28" s="52"/>
+      <c r="L28" s="55"/>
       <c r="M28" s="5">
         <v>8</v>
       </c>
@@ -18136,7 +18136,7 @@
       <c r="U28" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="W28" s="52"/>
+      <c r="W28" s="55"/>
       <c r="X28" s="5">
         <v>8</v>
       </c>
@@ -18166,7 +18166,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A29" s="52"/>
+      <c r="A29" s="55"/>
       <c r="B29" s="7">
         <v>8</v>
       </c>
@@ -18194,7 +18194,7 @@
       <c r="J29" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="L29" s="52"/>
+      <c r="L29" s="55"/>
       <c r="M29" s="7">
         <v>8</v>
       </c>
@@ -18222,7 +18222,7 @@
       <c r="U29" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="W29" s="52"/>
+      <c r="W29" s="55"/>
       <c r="X29" s="7">
         <v>8</v>
       </c>
@@ -18252,7 +18252,7 @@
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A30" s="52"/>
+      <c r="A30" s="55"/>
       <c r="B30" s="5">
         <v>8</v>
       </c>
@@ -18280,7 +18280,7 @@
       <c r="J30" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="L30" s="52"/>
+      <c r="L30" s="55"/>
       <c r="M30" s="5">
         <v>8</v>
       </c>
@@ -18308,7 +18308,7 @@
       <c r="U30" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="W30" s="52"/>
+      <c r="W30" s="55"/>
       <c r="X30" s="5">
         <v>8</v>
       </c>
@@ -18338,7 +18338,7 @@
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
+      <c r="A31" s="55"/>
       <c r="B31" s="7">
         <v>16</v>
       </c>
@@ -18366,7 +18366,7 @@
       <c r="J31" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="L31" s="52"/>
+      <c r="L31" s="55"/>
       <c r="M31" s="7">
         <v>16</v>
       </c>
@@ -18394,7 +18394,7 @@
       <c r="U31" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="W31" s="52"/>
+      <c r="W31" s="55"/>
       <c r="X31" s="7">
         <v>16</v>
       </c>
@@ -18424,7 +18424,7 @@
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A32" s="52"/>
+      <c r="A32" s="55"/>
       <c r="B32" s="5">
         <v>16</v>
       </c>
@@ -18452,7 +18452,7 @@
       <c r="J32" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="L32" s="52"/>
+      <c r="L32" s="55"/>
       <c r="M32" s="5">
         <v>16</v>
       </c>
@@ -18480,7 +18480,7 @@
       <c r="U32" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="W32" s="52"/>
+      <c r="W32" s="55"/>
       <c r="X32" s="5">
         <v>16</v>
       </c>
@@ -18510,7 +18510,7 @@
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
+      <c r="A33" s="55"/>
       <c r="B33" s="7">
         <v>16</v>
       </c>
@@ -18538,7 +18538,7 @@
       <c r="J33" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="L33" s="52"/>
+      <c r="L33" s="55"/>
       <c r="M33" s="7">
         <v>16</v>
       </c>
@@ -18566,7 +18566,7 @@
       <c r="U33" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="W33" s="52"/>
+      <c r="W33" s="55"/>
       <c r="X33" s="7">
         <v>16</v>
       </c>
@@ -18596,7 +18596,7 @@
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A34" s="52"/>
+      <c r="A34" s="55"/>
       <c r="B34" s="5">
         <v>16</v>
       </c>
@@ -18624,7 +18624,7 @@
       <c r="J34" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="L34" s="52"/>
+      <c r="L34" s="55"/>
       <c r="M34" s="5">
         <v>16</v>
       </c>
@@ -18652,7 +18652,7 @@
       <c r="U34" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="W34" s="52"/>
+      <c r="W34" s="55"/>
       <c r="X34" s="5">
         <v>16</v>
       </c>
@@ -18682,7 +18682,7 @@
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A35" s="52"/>
+      <c r="A35" s="55"/>
       <c r="B35" s="7">
         <v>24</v>
       </c>
@@ -18710,7 +18710,7 @@
       <c r="J35" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="L35" s="52"/>
+      <c r="L35" s="55"/>
       <c r="M35" s="7">
         <v>24</v>
       </c>
@@ -18738,7 +18738,7 @@
       <c r="U35" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="W35" s="52"/>
+      <c r="W35" s="55"/>
       <c r="X35" s="7">
         <v>24</v>
       </c>
@@ -18768,7 +18768,7 @@
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
+      <c r="A36" s="55"/>
       <c r="B36" s="5">
         <v>24</v>
       </c>
@@ -18796,7 +18796,7 @@
       <c r="J36" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="L36" s="52"/>
+      <c r="L36" s="55"/>
       <c r="M36" s="5">
         <v>24</v>
       </c>
@@ -18824,7 +18824,7 @@
       <c r="U36" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="W36" s="52"/>
+      <c r="W36" s="55"/>
       <c r="X36" s="5">
         <v>24</v>
       </c>
@@ -18854,7 +18854,7 @@
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
+      <c r="A37" s="55"/>
       <c r="B37" s="7">
         <v>24</v>
       </c>
@@ -18882,7 +18882,7 @@
       <c r="J37" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="L37" s="52"/>
+      <c r="L37" s="55"/>
       <c r="M37" s="7">
         <v>24</v>
       </c>
@@ -18910,7 +18910,7 @@
       <c r="U37" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="W37" s="52"/>
+      <c r="W37" s="55"/>
       <c r="X37" s="7">
         <v>24</v>
       </c>
@@ -18940,7 +18940,7 @@
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="52"/>
+      <c r="A38" s="55"/>
       <c r="B38" s="5">
         <v>24</v>
       </c>
@@ -18968,7 +18968,7 @@
       <c r="J38" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="L38" s="52"/>
+      <c r="L38" s="55"/>
       <c r="M38" s="5">
         <v>24</v>
       </c>
@@ -18996,7 +18996,7 @@
       <c r="U38" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="W38" s="52"/>
+      <c r="W38" s="55"/>
       <c r="X38" s="5">
         <v>24</v>
       </c>
@@ -19112,7 +19112,7 @@
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="55" t="s">
         <v>299</v>
       </c>
       <c r="B40" s="3">
@@ -19142,7 +19142,7 @@
       <c r="J40" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="L40" s="52" t="s">
+      <c r="L40" s="55" t="s">
         <v>299</v>
       </c>
       <c r="M40" s="3">
@@ -19172,7 +19172,7 @@
       <c r="U40" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="W40" s="52" t="s">
+      <c r="W40" s="55" t="s">
         <v>299</v>
       </c>
       <c r="X40" s="3">
@@ -19204,7 +19204,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A41" s="52"/>
+      <c r="A41" s="55"/>
       <c r="B41" s="5">
         <v>1</v>
       </c>
@@ -19232,7 +19232,7 @@
       <c r="J41" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="L41" s="52"/>
+      <c r="L41" s="55"/>
       <c r="M41" s="5">
         <v>1</v>
       </c>
@@ -19260,7 +19260,7 @@
       <c r="U41" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="W41" s="52"/>
+      <c r="W41" s="55"/>
       <c r="X41" s="5">
         <v>1</v>
       </c>
@@ -19290,7 +19290,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A42" s="52"/>
+      <c r="A42" s="55"/>
       <c r="B42" s="7">
         <v>1</v>
       </c>
@@ -19318,7 +19318,7 @@
       <c r="J42" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="L42" s="52"/>
+      <c r="L42" s="55"/>
       <c r="M42" s="7">
         <v>1</v>
       </c>
@@ -19346,7 +19346,7 @@
       <c r="U42" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="W42" s="52"/>
+      <c r="W42" s="55"/>
       <c r="X42" s="7">
         <v>1</v>
       </c>
@@ -19376,7 +19376,7 @@
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="52"/>
+      <c r="A43" s="55"/>
       <c r="B43" s="5">
         <v>1</v>
       </c>
@@ -19404,7 +19404,7 @@
       <c r="J43" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="L43" s="52"/>
+      <c r="L43" s="55"/>
       <c r="M43" s="5">
         <v>1</v>
       </c>
@@ -19432,7 +19432,7 @@
       <c r="U43" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="W43" s="52"/>
+      <c r="W43" s="55"/>
       <c r="X43" s="5">
         <v>1</v>
       </c>
@@ -19462,7 +19462,7 @@
       </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A44" s="52"/>
+      <c r="A44" s="55"/>
       <c r="B44" s="7">
         <v>2</v>
       </c>
@@ -19490,7 +19490,7 @@
       <c r="J44" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="L44" s="52"/>
+      <c r="L44" s="55"/>
       <c r="M44" s="7">
         <v>2</v>
       </c>
@@ -19518,7 +19518,7 @@
       <c r="U44" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="W44" s="52"/>
+      <c r="W44" s="55"/>
       <c r="X44" s="7">
         <v>2</v>
       </c>
@@ -19548,7 +19548,7 @@
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A45" s="52"/>
+      <c r="A45" s="55"/>
       <c r="B45" s="5">
         <v>2</v>
       </c>
@@ -19576,7 +19576,7 @@
       <c r="J45" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="L45" s="52"/>
+      <c r="L45" s="55"/>
       <c r="M45" s="5">
         <v>2</v>
       </c>
@@ -19604,7 +19604,7 @@
       <c r="U45" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="W45" s="52"/>
+      <c r="W45" s="55"/>
       <c r="X45" s="5">
         <v>2</v>
       </c>
@@ -19634,7 +19634,7 @@
       </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A46" s="52"/>
+      <c r="A46" s="55"/>
       <c r="B46" s="7">
         <v>2</v>
       </c>
@@ -19662,7 +19662,7 @@
       <c r="J46" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="L46" s="52"/>
+      <c r="L46" s="55"/>
       <c r="M46" s="7">
         <v>2</v>
       </c>
@@ -19690,7 +19690,7 @@
       <c r="U46" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="W46" s="52"/>
+      <c r="W46" s="55"/>
       <c r="X46" s="7">
         <v>2</v>
       </c>
@@ -19720,7 +19720,7 @@
       </c>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A47" s="52"/>
+      <c r="A47" s="55"/>
       <c r="B47" s="5">
         <v>2</v>
       </c>
@@ -19748,7 +19748,7 @@
       <c r="J47" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="L47" s="52"/>
+      <c r="L47" s="55"/>
       <c r="M47" s="5">
         <v>2</v>
       </c>
@@ -19776,7 +19776,7 @@
       <c r="U47" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="W47" s="52"/>
+      <c r="W47" s="55"/>
       <c r="X47" s="5">
         <v>2</v>
       </c>
@@ -19806,7 +19806,7 @@
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A48" s="52"/>
+      <c r="A48" s="55"/>
       <c r="B48" s="7">
         <v>4</v>
       </c>
@@ -19834,7 +19834,7 @@
       <c r="J48" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="L48" s="52"/>
+      <c r="L48" s="55"/>
       <c r="M48" s="7">
         <v>4</v>
       </c>
@@ -19862,7 +19862,7 @@
       <c r="U48" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="W48" s="52"/>
+      <c r="W48" s="55"/>
       <c r="X48" s="7">
         <v>4</v>
       </c>
@@ -19892,7 +19892,7 @@
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A49" s="52"/>
+      <c r="A49" s="55"/>
       <c r="B49" s="5">
         <v>4</v>
       </c>
@@ -19920,7 +19920,7 @@
       <c r="J49" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="L49" s="52"/>
+      <c r="L49" s="55"/>
       <c r="M49" s="5">
         <v>4</v>
       </c>
@@ -19948,7 +19948,7 @@
       <c r="U49" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="W49" s="52"/>
+      <c r="W49" s="55"/>
       <c r="X49" s="5">
         <v>4</v>
       </c>
@@ -19978,7 +19978,7 @@
       </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A50" s="52"/>
+      <c r="A50" s="55"/>
       <c r="B50" s="7">
         <v>4</v>
       </c>
@@ -20006,7 +20006,7 @@
       <c r="J50" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="L50" s="52"/>
+      <c r="L50" s="55"/>
       <c r="M50" s="7">
         <v>4</v>
       </c>
@@ -20034,7 +20034,7 @@
       <c r="U50" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="W50" s="52"/>
+      <c r="W50" s="55"/>
       <c r="X50" s="7">
         <v>4</v>
       </c>
@@ -20064,7 +20064,7 @@
       </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A51" s="52"/>
+      <c r="A51" s="55"/>
       <c r="B51" s="5">
         <v>4</v>
       </c>
@@ -20092,7 +20092,7 @@
       <c r="J51" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="L51" s="52"/>
+      <c r="L51" s="55"/>
       <c r="M51" s="5">
         <v>4</v>
       </c>
@@ -20120,7 +20120,7 @@
       <c r="U51" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="W51" s="52"/>
+      <c r="W51" s="55"/>
       <c r="X51" s="5">
         <v>4</v>
       </c>
@@ -20150,7 +20150,7 @@
       </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A52" s="52"/>
+      <c r="A52" s="55"/>
       <c r="B52" s="7">
         <v>8</v>
       </c>
@@ -20178,7 +20178,7 @@
       <c r="J52" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="L52" s="52"/>
+      <c r="L52" s="55"/>
       <c r="M52" s="7">
         <v>8</v>
       </c>
@@ -20206,7 +20206,7 @@
       <c r="U52" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="W52" s="52"/>
+      <c r="W52" s="55"/>
       <c r="X52" s="7">
         <v>8</v>
       </c>
@@ -20236,7 +20236,7 @@
       </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A53" s="52"/>
+      <c r="A53" s="55"/>
       <c r="B53" s="5">
         <v>8</v>
       </c>
@@ -20264,7 +20264,7 @@
       <c r="J53" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="L53" s="52"/>
+      <c r="L53" s="55"/>
       <c r="M53" s="5">
         <v>8</v>
       </c>
@@ -20292,7 +20292,7 @@
       <c r="U53" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="W53" s="52"/>
+      <c r="W53" s="55"/>
       <c r="X53" s="5">
         <v>8</v>
       </c>
@@ -20322,7 +20322,7 @@
       </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A54" s="52"/>
+      <c r="A54" s="55"/>
       <c r="B54" s="7">
         <v>8</v>
       </c>
@@ -20350,7 +20350,7 @@
       <c r="J54" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="L54" s="52"/>
+      <c r="L54" s="55"/>
       <c r="M54" s="7">
         <v>8</v>
       </c>
@@ -20378,7 +20378,7 @@
       <c r="U54" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="W54" s="52"/>
+      <c r="W54" s="55"/>
       <c r="X54" s="7">
         <v>8</v>
       </c>
@@ -20408,7 +20408,7 @@
       </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A55" s="52"/>
+      <c r="A55" s="55"/>
       <c r="B55" s="5">
         <v>8</v>
       </c>
@@ -20436,7 +20436,7 @@
       <c r="J55" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="L55" s="52"/>
+      <c r="L55" s="55"/>
       <c r="M55" s="5">
         <v>8</v>
       </c>
@@ -20464,7 +20464,7 @@
       <c r="U55" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="W55" s="52"/>
+      <c r="W55" s="55"/>
       <c r="X55" s="5">
         <v>8</v>
       </c>
@@ -20494,7 +20494,7 @@
       </c>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A56" s="52"/>
+      <c r="A56" s="55"/>
       <c r="B56" s="7">
         <v>24</v>
       </c>
@@ -20522,7 +20522,7 @@
       <c r="J56" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="L56" s="52"/>
+      <c r="L56" s="55"/>
       <c r="M56" s="7">
         <v>24</v>
       </c>
@@ -20550,7 +20550,7 @@
       <c r="U56" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="W56" s="52"/>
+      <c r="W56" s="55"/>
       <c r="X56" s="7">
         <v>24</v>
       </c>
@@ -20580,7 +20580,7 @@
       </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A57" s="52"/>
+      <c r="A57" s="55"/>
       <c r="B57" s="5">
         <v>24</v>
       </c>
@@ -20608,7 +20608,7 @@
       <c r="J57" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="L57" s="52"/>
+      <c r="L57" s="55"/>
       <c r="M57" s="5">
         <v>24</v>
       </c>
@@ -20636,7 +20636,7 @@
       <c r="U57" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="W57" s="52"/>
+      <c r="W57" s="55"/>
       <c r="X57" s="5">
         <v>24</v>
       </c>
@@ -20666,7 +20666,7 @@
       </c>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A58" s="52"/>
+      <c r="A58" s="55"/>
       <c r="B58" s="7">
         <v>24</v>
       </c>
@@ -20694,7 +20694,7 @@
       <c r="J58" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="L58" s="52"/>
+      <c r="L58" s="55"/>
       <c r="M58" s="7">
         <v>24</v>
       </c>
@@ -20722,7 +20722,7 @@
       <c r="U58" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="W58" s="52"/>
+      <c r="W58" s="55"/>
       <c r="X58" s="7">
         <v>24</v>
       </c>
@@ -20752,7 +20752,7 @@
       </c>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A59" s="52"/>
+      <c r="A59" s="55"/>
       <c r="B59" s="5">
         <v>24</v>
       </c>
@@ -20780,7 +20780,7 @@
       <c r="J59" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="L59" s="52"/>
+      <c r="L59" s="55"/>
       <c r="M59" s="5">
         <v>24</v>
       </c>
@@ -20808,7 +20808,7 @@
       <c r="U59" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="W59" s="52"/>
+      <c r="W59" s="55"/>
       <c r="X59" s="5">
         <v>24</v>
       </c>
@@ -20924,7 +20924,7 @@
       </c>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A61" s="52" t="s">
+      <c r="A61" s="55" t="s">
         <v>438</v>
       </c>
       <c r="B61" s="3">
@@ -20954,7 +20954,7 @@
       <c r="J61" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="L61" s="52" t="s">
+      <c r="L61" s="55" t="s">
         <v>438</v>
       </c>
       <c r="M61" s="3">
@@ -20984,7 +20984,7 @@
       <c r="U61" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="W61" s="52" t="s">
+      <c r="W61" s="55" t="s">
         <v>438</v>
       </c>
       <c r="X61" s="3">
@@ -21016,7 +21016,7 @@
       </c>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A62" s="52"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="5">
         <v>4</v>
       </c>
@@ -21044,7 +21044,7 @@
       <c r="J62" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="L62" s="52"/>
+      <c r="L62" s="55"/>
       <c r="M62" s="5">
         <v>4</v>
       </c>
@@ -21072,7 +21072,7 @@
       <c r="U62" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="W62" s="52"/>
+      <c r="W62" s="55"/>
       <c r="X62" s="5">
         <v>4</v>
       </c>
@@ -21102,7 +21102,7 @@
       </c>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A63" s="52"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="7">
         <v>4</v>
       </c>
@@ -21130,7 +21130,7 @@
       <c r="J63" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="L63" s="52"/>
+      <c r="L63" s="55"/>
       <c r="M63" s="7">
         <v>4</v>
       </c>
@@ -21158,7 +21158,7 @@
       <c r="U63" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="W63" s="52"/>
+      <c r="W63" s="55"/>
       <c r="X63" s="7">
         <v>4</v>
       </c>
@@ -21188,7 +21188,7 @@
       </c>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A64" s="52"/>
+      <c r="A64" s="55"/>
       <c r="B64" s="5">
         <v>4</v>
       </c>
@@ -21216,7 +21216,7 @@
       <c r="J64" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="L64" s="52"/>
+      <c r="L64" s="55"/>
       <c r="M64" s="5">
         <v>4</v>
       </c>
@@ -21244,7 +21244,7 @@
       <c r="U64" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="W64" s="52"/>
+      <c r="W64" s="55"/>
       <c r="X64" s="5">
         <v>4</v>
       </c>
@@ -21274,7 +21274,7 @@
       </c>
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A65" s="52"/>
+      <c r="A65" s="55"/>
       <c r="B65" s="7">
         <v>8</v>
       </c>
@@ -21302,7 +21302,7 @@
       <c r="J65" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="L65" s="52"/>
+      <c r="L65" s="55"/>
       <c r="M65" s="7">
         <v>8</v>
       </c>
@@ -21330,7 +21330,7 @@
       <c r="U65" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="W65" s="52"/>
+      <c r="W65" s="55"/>
       <c r="X65" s="7">
         <v>8</v>
       </c>
@@ -21360,7 +21360,7 @@
       </c>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A66" s="52"/>
+      <c r="A66" s="55"/>
       <c r="B66" s="5">
         <v>8</v>
       </c>
@@ -21388,7 +21388,7 @@
       <c r="J66" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="L66" s="52"/>
+      <c r="L66" s="55"/>
       <c r="M66" s="5">
         <v>8</v>
       </c>
@@ -21416,7 +21416,7 @@
       <c r="U66" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="W66" s="52"/>
+      <c r="W66" s="55"/>
       <c r="X66" s="5">
         <v>8</v>
       </c>
@@ -21446,7 +21446,7 @@
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A67" s="52"/>
+      <c r="A67" s="55"/>
       <c r="B67" s="7">
         <v>8</v>
       </c>
@@ -21474,7 +21474,7 @@
       <c r="J67" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="L67" s="52"/>
+      <c r="L67" s="55"/>
       <c r="M67" s="7">
         <v>8</v>
       </c>
@@ -21502,7 +21502,7 @@
       <c r="U67" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="W67" s="52"/>
+      <c r="W67" s="55"/>
       <c r="X67" s="7">
         <v>8</v>
       </c>
@@ -21532,7 +21532,7 @@
       </c>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A68" s="52"/>
+      <c r="A68" s="55"/>
       <c r="B68" s="5">
         <v>8</v>
       </c>
@@ -21560,7 +21560,7 @@
       <c r="J68" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="L68" s="52"/>
+      <c r="L68" s="55"/>
       <c r="M68" s="5">
         <v>8</v>
       </c>
@@ -21588,7 +21588,7 @@
       <c r="U68" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="W68" s="52"/>
+      <c r="W68" s="55"/>
       <c r="X68" s="5">
         <v>8</v>
       </c>
@@ -21618,7 +21618,7 @@
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A69" s="52"/>
+      <c r="A69" s="55"/>
       <c r="B69" s="7">
         <v>12</v>
       </c>
@@ -21646,7 +21646,7 @@
       <c r="J69" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="L69" s="52"/>
+      <c r="L69" s="55"/>
       <c r="M69" s="7">
         <v>12</v>
       </c>
@@ -21674,7 +21674,7 @@
       <c r="U69" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="W69" s="52"/>
+      <c r="W69" s="55"/>
       <c r="X69" s="7">
         <v>12</v>
       </c>
@@ -21704,7 +21704,7 @@
       </c>
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A70" s="52"/>
+      <c r="A70" s="55"/>
       <c r="B70" s="5">
         <v>12</v>
       </c>
@@ -21732,7 +21732,7 @@
       <c r="J70" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="L70" s="52"/>
+      <c r="L70" s="55"/>
       <c r="M70" s="5">
         <v>12</v>
       </c>
@@ -21760,7 +21760,7 @@
       <c r="U70" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="W70" s="52"/>
+      <c r="W70" s="55"/>
       <c r="X70" s="5">
         <v>12</v>
       </c>
@@ -21790,7 +21790,7 @@
       </c>
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A71" s="52"/>
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>12</v>
       </c>
@@ -21819,7 +21819,7 @@
         <v>256</v>
       </c>
       <c r="K71" s="10"/>
-      <c r="L71" s="52"/>
+      <c r="L71" s="55"/>
       <c r="M71" s="7">
         <v>12</v>
       </c>
@@ -21847,7 +21847,7 @@
       <c r="U71" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="W71" s="52"/>
+      <c r="W71" s="55"/>
       <c r="X71" s="7">
         <v>12</v>
       </c>
@@ -21877,7 +21877,7 @@
       </c>
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A72" s="52"/>
+      <c r="A72" s="55"/>
       <c r="B72" s="5">
         <v>12</v>
       </c>
@@ -21905,7 +21905,7 @@
       <c r="J72" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="L72" s="52"/>
+      <c r="L72" s="55"/>
       <c r="M72" s="5">
         <v>12</v>
       </c>
@@ -21933,7 +21933,7 @@
       <c r="U72" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="W72" s="52"/>
+      <c r="W72" s="55"/>
       <c r="X72" s="5">
         <v>12</v>
       </c>
@@ -22049,7 +22049,7 @@
       </c>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A74" s="52" t="s">
+      <c r="A74" s="55" t="s">
         <v>511</v>
       </c>
       <c r="B74" s="3">
@@ -22079,7 +22079,7 @@
       <c r="J74" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="L74" s="52" t="s">
+      <c r="L74" s="55" t="s">
         <v>511</v>
       </c>
       <c r="M74" s="3">
@@ -22109,7 +22109,7 @@
       <c r="U74" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="W74" s="52" t="s">
+      <c r="W74" s="55" t="s">
         <v>511</v>
       </c>
       <c r="X74" s="3">
@@ -22141,7 +22141,7 @@
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A75" s="52"/>
+      <c r="A75" s="55"/>
       <c r="B75" s="5">
         <v>0</v>
       </c>
@@ -22169,7 +22169,7 @@
       <c r="J75" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="L75" s="52"/>
+      <c r="L75" s="55"/>
       <c r="M75" s="5">
         <v>0</v>
       </c>
@@ -22197,7 +22197,7 @@
       <c r="U75" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="W75" s="52"/>
+      <c r="W75" s="55"/>
       <c r="X75" s="5">
         <v>0</v>
       </c>
@@ -22227,7 +22227,7 @@
       </c>
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A76" s="52"/>
+      <c r="A76" s="55"/>
       <c r="B76" s="7">
         <v>0</v>
       </c>
@@ -22255,7 +22255,7 @@
       <c r="J76" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="L76" s="52"/>
+      <c r="L76" s="55"/>
       <c r="M76" s="7">
         <v>0</v>
       </c>
@@ -22283,7 +22283,7 @@
       <c r="U76" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="W76" s="52"/>
+      <c r="W76" s="55"/>
       <c r="X76" s="7">
         <v>0</v>
       </c>
@@ -22313,7 +22313,7 @@
       </c>
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A77" s="52"/>
+      <c r="A77" s="55"/>
       <c r="B77" s="5">
         <v>0</v>
       </c>
@@ -22341,7 +22341,7 @@
       <c r="J77" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="L77" s="52"/>
+      <c r="L77" s="55"/>
       <c r="M77" s="5">
         <v>0</v>
       </c>
@@ -22369,7 +22369,7 @@
       <c r="U77" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="W77" s="52"/>
+      <c r="W77" s="55"/>
       <c r="X77" s="5">
         <v>0</v>
       </c>
@@ -22400,6 +22400,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="L2:L21"/>
+    <mergeCell ref="W2:W21"/>
+    <mergeCell ref="A23:A38"/>
+    <mergeCell ref="L23:L38"/>
+    <mergeCell ref="W23:W38"/>
     <mergeCell ref="A74:A77"/>
     <mergeCell ref="L74:L77"/>
     <mergeCell ref="W74:W77"/>
@@ -22409,12 +22415,6 @@
     <mergeCell ref="A61:A72"/>
     <mergeCell ref="L61:L72"/>
     <mergeCell ref="W61:W72"/>
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="L2:L21"/>
-    <mergeCell ref="W2:W21"/>
-    <mergeCell ref="A23:A38"/>
-    <mergeCell ref="L23:L38"/>
-    <mergeCell ref="W23:W38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27867,51 +27867,51 @@
       <c r="B1" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="S1" s="56" t="s">
+      <c r="S1" s="50" t="s">
         <v>543</v>
       </c>
-      <c r="T1" s="56"/>
-      <c r="U1" s="55" t="s">
+      <c r="T1" s="50"/>
+      <c r="U1" s="48" t="s">
         <v>544</v>
       </c>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55" t="s">
+      <c r="V1" s="48"/>
+      <c r="W1" s="48" t="s">
         <v>545</v>
       </c>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55" t="s">
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48" t="s">
         <v>546</v>
       </c>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55" t="s">
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48" t="s">
         <v>547</v>
       </c>
-      <c r="AB1" s="55"/>
+      <c r="AB1" s="48"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="53">
         <v>1</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>548</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="52" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51" t="s">
+      <c r="F2" s="52"/>
+      <c r="G2" s="52" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="52"/>
       <c r="K2" s="15" t="s">
         <v>552</v>
       </c>
@@ -27924,10 +27924,10 @@
       <c r="N2" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="S2" s="55" t="s">
+      <c r="S2" s="48" t="s">
         <v>556</v>
       </c>
-      <c r="T2" s="55"/>
+      <c r="T2" s="48"/>
       <c r="U2" s="26" t="s">
         <v>557</v>
       </c>
@@ -27954,17 +27954,17 @@
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="54"/>
-      <c r="D3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="E3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="G3" s="51"/>
+      <c r="G3" s="52"/>
       <c r="H3" s="13" t="s">
         <v>557</v>
       </c>
@@ -27984,13 +27984,13 @@
         <f t="array" ref="N3">INDEX(DropDowns!I2:I10, MATCH(A2&amp;B2, DropDowns!E2:E10&amp;DropDowns!F2:F10, 0))</f>
         <v>5.27</v>
       </c>
-      <c r="O3" s="50" t="s">
+      <c r="O3" s="51" t="s">
         <v>559</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="P3" s="51" t="s">
         <v>560</v>
       </c>
-      <c r="Q3" s="50" t="s">
+      <c r="Q3" s="51" t="s">
         <v>561</v>
       </c>
       <c r="R3" s="21"/>
@@ -28074,9 +28074,9 @@
       <c r="N4" s="25" t="s">
         <v>566</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="21"/>
       <c r="S4" s="26">
         <v>2</v>
@@ -28738,10 +28738,10 @@
         <f>SUM(N5:N12)</f>
         <v>96433.802258765791</v>
       </c>
-      <c r="O13" s="53" t="s">
+      <c r="O13" s="49" t="s">
         <v>575</v>
       </c>
-      <c r="P13" s="53"/>
+      <c r="P13" s="49"/>
       <c r="Q13" s="28">
         <f>N13 + SUM(Q5:Q12)</f>
         <v>2376658933.802259</v>
@@ -29930,12 +29930,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="S1:T1"/>
     <mergeCell ref="O13:P13"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -29947,6 +29941,12 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="S1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29992,45 +29992,45 @@
       <c r="B1" s="14" t="s">
         <v>580</v>
       </c>
-      <c r="S1" s="56" t="s">
+      <c r="S1" s="50" t="s">
         <v>543</v>
       </c>
-      <c r="T1" s="56"/>
-      <c r="U1" s="55" t="s">
+      <c r="T1" s="50"/>
+      <c r="U1" s="48" t="s">
         <v>550</v>
       </c>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="53">
         <v>4</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>540</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="52" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51" t="s">
+      <c r="F2" s="52"/>
+      <c r="G2" s="52" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="52"/>
       <c r="K2" s="15" t="s">
         <v>552</v>
       </c>
@@ -30043,10 +30043,10 @@
       <c r="N2" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="S2" s="55" t="s">
+      <c r="S2" s="48" t="s">
         <v>556</v>
       </c>
-      <c r="T2" s="55"/>
+      <c r="T2" s="48"/>
       <c r="U2" s="26" t="s">
         <v>557</v>
       </c>
@@ -30061,17 +30061,17 @@
       <c r="AB2" s="26"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="54"/>
-      <c r="D3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="E3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="G3" s="51"/>
+      <c r="G3" s="52"/>
       <c r="H3" s="13" t="s">
         <v>557</v>
       </c>
@@ -30091,13 +30091,13 @@
         <f t="array" ref="N3">INDEX(DropDowns!O2:O10, MATCH(A2&amp;B2, DropDowns!K2:K10&amp;DropDowns!L2:L10, 0))</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="O3" s="50" t="s">
+      <c r="O3" s="51" t="s">
         <v>559</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="P3" s="51" t="s">
         <v>560</v>
       </c>
-      <c r="Q3" s="50" t="s">
+      <c r="Q3" s="51" t="s">
         <v>561</v>
       </c>
       <c r="S3" s="26">
@@ -30160,9 +30160,9 @@
       <c r="N4" s="25" t="s">
         <v>566</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
       <c r="S4" s="26">
         <v>1</v>
       </c>
@@ -30471,10 +30471,10 @@
         <f>SUM(N5:N8)</f>
         <v>133543.23813618615</v>
       </c>
-      <c r="O9" s="53" t="s">
+      <c r="O9" s="49" t="s">
         <v>575</v>
       </c>
-      <c r="P9" s="53"/>
+      <c r="P9" s="49"/>
       <c r="Q9" s="28">
         <f>N9 + SUM(Q5:Q8)</f>
         <v>133543.23813618615</v>
@@ -31287,6 +31287,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:G3"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="S2:T2"/>
@@ -31297,13 +31304,6 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31349,29 +31349,29 @@
       </c>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="53">
         <v>16</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>540</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="52" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51" t="s">
+      <c r="F2" s="52"/>
+      <c r="G2" s="52" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="52"/>
       <c r="AN2" s="21"/>
       <c r="AO2" s="22"/>
       <c r="AP2" s="22"/>
@@ -31381,17 +31381,17 @@
       <c r="AT2" s="22"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="54"/>
-      <c r="D3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="E3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="G3" s="51"/>
+      <c r="G3" s="52"/>
       <c r="H3" s="13" t="s">
         <v>557</v>
       </c>
@@ -31581,36 +31581,36 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>298</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="52" t="s">
         <v>549</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="52" t="s">
         <v>586</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="F3" s="51"/>
+      <c r="F3" s="52"/>
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
     </row>
@@ -32477,26 +32477,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="771465c8-566f-4c1b-b214-95c896f401f4" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6656c2dc-2965-4315-a8fd-a4d95559af9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100309D7ACAE19AEA4188E74FC911064806" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e8a604d3f0bb0e89f6632cd1c645b4ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6656c2dc-2965-4315-a8fd-a4d95559af9c" xmlns:ns3="771465c8-566f-4c1b-b214-95c896f401f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb3c6b3dfa206ae2f3e4fe521c8aca1a" ns2:_="" ns3:_="">
     <xsd:import namespace="6656c2dc-2965-4315-a8fd-a4d95559af9c"/>
@@ -32697,10 +32677,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="771465c8-566f-4c1b-b214-95c896f401f4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6656c2dc-2965-4315-a8fd-a4d95559af9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26E5D28-D9FA-4066-B241-E5CE1A22D21C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3751360D-7852-429C-A040-28D5BB8F3663}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6656c2dc-2965-4315-a8fd-a4d95559af9c"/>
+    <ds:schemaRef ds:uri="771465c8-566f-4c1b-b214-95c896f401f4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -32723,20 +32734,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3751360D-7852-429C-A040-28D5BB8F3663}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26E5D28-D9FA-4066-B241-E5CE1A22D21C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6656c2dc-2965-4315-a8fd-a4d95559af9c"/>
-    <ds:schemaRef ds:uri="771465c8-566f-4c1b-b214-95c896f401f4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Scaling Tests.xlsx
+++ b/Scaling Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MGT-2025-26\MGT-Thesis-Repository\MGT-Thesis-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0B250F-5303-4254-BA2A-059F9699D35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AAB58A-39A7-4034-B488-76B459D9242B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -2154,23 +2154,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -27867,10 +27867,10 @@
       <c r="B1" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="S1" s="50" t="s">
+      <c r="S1" s="49" t="s">
         <v>543</v>
       </c>
-      <c r="T1" s="50"/>
+      <c r="T1" s="49"/>
       <c r="U1" s="48" t="s">
         <v>544</v>
       </c>
@@ -27889,29 +27889,29 @@
       <c r="AB1" s="48"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="53">
-        <v>1</v>
-      </c>
-      <c r="C2" s="54" t="s">
+      <c r="B2" s="52">
+        <v>1</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>548</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="54" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52" t="s">
+      <c r="F2" s="54"/>
+      <c r="G2" s="54" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="I2" s="52"/>
+      <c r="I2" s="54"/>
       <c r="K2" s="15" t="s">
         <v>552</v>
       </c>
@@ -27954,17 +27954,17 @@
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="52"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="G3" s="52"/>
+      <c r="G3" s="54"/>
       <c r="H3" s="13" t="s">
         <v>557</v>
       </c>
@@ -28738,10 +28738,10 @@
         <f>SUM(N5:N12)</f>
         <v>96433.802258765791</v>
       </c>
-      <c r="O13" s="49" t="s">
+      <c r="O13" s="50" t="s">
         <v>575</v>
       </c>
-      <c r="P13" s="49"/>
+      <c r="P13" s="50"/>
       <c r="Q13" s="28">
         <f>N13 + SUM(Q5:Q12)</f>
         <v>2376658933.802259</v>
@@ -29992,10 +29992,10 @@
       <c r="B1" s="14" t="s">
         <v>580</v>
       </c>
-      <c r="S1" s="50" t="s">
+      <c r="S1" s="49" t="s">
         <v>543</v>
       </c>
-      <c r="T1" s="50"/>
+      <c r="T1" s="49"/>
       <c r="U1" s="48" t="s">
         <v>550</v>
       </c>
@@ -30008,29 +30008,29 @@
       <c r="AB1" s="48"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="52">
         <v>4</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="53" t="s">
         <v>540</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="54" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52" t="s">
+      <c r="F2" s="54"/>
+      <c r="G2" s="54" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="I2" s="52"/>
+      <c r="I2" s="54"/>
       <c r="K2" s="15" t="s">
         <v>552</v>
       </c>
@@ -30061,17 +30061,17 @@
       <c r="AB2" s="26"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="52"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="G3" s="52"/>
+      <c r="G3" s="54"/>
       <c r="H3" s="13" t="s">
         <v>557</v>
       </c>
@@ -30080,15 +30080,15 @@
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="27" cm="1">
-        <f t="array" ref="L3">INDEX(DropDowns!M2:M10, MATCH(A2&amp;B2, DropDowns!K2:K10&amp;DropDowns!L2:L10, 0))</f>
+        <f t="array" ref="L3">INDEX(DropDowns!M2:M22, MATCH(A2&amp;B2, DropDowns!K2:K22&amp;DropDowns!L2:L22, 0))</f>
         <v>1718.98</v>
       </c>
       <c r="M3" s="28" cm="1">
-        <f t="array" ref="M3">INDEX(DropDowns!N2:N10, MATCH(A2&amp;B2, DropDowns!K2:K10&amp;DropDowns!L2:L10, 0))</f>
+        <f t="array" ref="M3">INDEX(DropDowns!N2:N22, MATCH(A2&amp;B2, DropDowns!K2:K22&amp;DropDowns!L2:L22, 0))</f>
         <v>9883.08</v>
       </c>
       <c r="N3" s="29" cm="1">
-        <f t="array" ref="N3">INDEX(DropDowns!O2:O10, MATCH(A2&amp;B2, DropDowns!K2:K10&amp;DropDowns!L2:L10, 0))</f>
+        <f t="array" ref="N3">INDEX(DropDowns!O2:O22, MATCH(A2&amp;B2, DropDowns!K2:K22&amp;DropDowns!L2:L22, 0))</f>
         <v>1.1100000000000001</v>
       </c>
       <c r="O3" s="51" t="s">
@@ -30471,10 +30471,10 @@
         <f>SUM(N5:N8)</f>
         <v>133543.23813618615</v>
       </c>
-      <c r="O9" s="49" t="s">
+      <c r="O9" s="50" t="s">
         <v>575</v>
       </c>
-      <c r="P9" s="49"/>
+      <c r="P9" s="50"/>
       <c r="Q9" s="28">
         <f>N9 + SUM(Q5:Q8)</f>
         <v>133543.23813618615</v>
@@ -31349,29 +31349,29 @@
       </c>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="52">
         <v>16</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="53" t="s">
         <v>540</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="54" t="s">
         <v>549</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52" t="s">
+      <c r="F2" s="54"/>
+      <c r="G2" s="54" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="I2" s="52"/>
+      <c r="I2" s="54"/>
       <c r="AN2" s="21"/>
       <c r="AO2" s="22"/>
       <c r="AP2" s="22"/>
@@ -31381,17 +31381,17 @@
       <c r="AT2" s="22"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="52"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="G3" s="52"/>
+      <c r="G3" s="54"/>
       <c r="H3" s="13" t="s">
         <v>557</v>
       </c>
@@ -31581,36 +31581,36 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="52" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="51" t="s">
         <v>298</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="54" t="s">
         <v>549</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52" t="s">
+      <c r="E2" s="54"/>
+      <c r="F2" s="54" t="s">
         <v>586</v>
       </c>
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
+      <c r="A3" s="52"/>
       <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="13" t="s">
         <v>557</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="F3" s="52"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
     </row>
